--- a/reports/Debug-purgatory-20260111/Month to Date (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260111/Month to Date (Actual)_Budget.xlsx
@@ -40,84 +40,99 @@
     <t>D8040</t>
   </si>
   <si>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5205</t>
+  </si>
+  <si>
+    <t>D5207</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4056</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D5810</t>
+  </si>
+  <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4054</t>
+  </si>
+  <si>
+    <t>D5206</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
     <t>D6780</t>
   </si>
   <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4056</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D5810</t>
-  </si>
-  <si>
     <t>99200</t>
   </si>
   <si>
     <t>D8050</t>
   </si>
   <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4054</t>
-  </si>
-  <si>
-    <t>D5206</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6720</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D6800</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D4053</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5205</t>
-  </si>
-  <si>
-    <t>D5207</t>
-  </si>
-  <si>
-    <t>D6710</t>
-  </si>
-  <si>
-    <t>D6750</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
     <t>99100</t>
   </si>
   <si>
@@ -142,21 +157,6 @@
     <t>D8020</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D6212</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -196,84 +196,99 @@
     <t>HR</t>
   </si>
   <si>
+    <t>Lift Operations</t>
+  </si>
+  <si>
+    <t>Terrain Park</t>
+  </si>
+  <si>
+    <t>Ski Patrol</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>Expert Edge</t>
+  </si>
+  <si>
+    <t>Purg Sports Main Ave</t>
+  </si>
+  <si>
+    <t>Waffle Cabin</t>
+  </si>
+  <si>
+    <t>Paradise</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Lift Maintenance</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Branded</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Mountain G&amp;A</t>
+  </si>
+  <si>
+    <t>Purg Sports Resort</t>
+  </si>
+  <si>
+    <t>Hoody's</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Guest Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Branded</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
     <t>Winter Season Pass Visits  - Home Resort</t>
   </si>
   <si>
     <t>Risk Management</t>
   </si>
   <si>
-    <t>Mountain G&amp;A</t>
-  </si>
-  <si>
-    <t>Purg Sports Resort</t>
-  </si>
-  <si>
-    <t>Hoody's</t>
-  </si>
-  <si>
-    <t>Resort Services G&amp;A</t>
-  </si>
-  <si>
-    <t>Guest Services</t>
-  </si>
-  <si>
-    <t>Security</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Commercial Tenants</t>
-  </si>
-  <si>
-    <t>Lift Operations</t>
-  </si>
-  <si>
-    <t>Terrain Park</t>
-  </si>
-  <si>
-    <t>Ski Patrol</t>
-  </si>
-  <si>
-    <t>Tickets</t>
-  </si>
-  <si>
-    <t>Expert Edge</t>
-  </si>
-  <si>
-    <t>Purg Sports Main Ave</t>
-  </si>
-  <si>
-    <t>Waffle Cabin</t>
-  </si>
-  <si>
-    <t>Paradise</t>
-  </si>
-  <si>
-    <t>Accounting/Mgmt Services</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>IT Services</t>
-  </si>
-  <si>
     <t>Daily Winter Ticketed</t>
   </si>
   <si>
@@ -296,21 +311,6 @@
   </si>
   <si>
     <t>Accounting</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
-  </si>
-  <si>
-    <t>Functions</t>
-  </si>
-  <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
         <v>50</v>
       </c>
       <c r="C6" s="2">
-        <v>73895.70</v>
+        <v>70759.64</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>56</v>
@@ -813,10 +813,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2">
-        <v>5103.81</v>
+        <v>56833.27</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>60</v>
@@ -824,128 +824,128 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="2">
-        <v>24178.10</v>
+        <v>8452.20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C12" s="2">
-        <v>8369.80</v>
+        <v>50141.18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2">
-        <v>66784.07</v>
+        <v>13439.63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2">
-        <v>2182.50</v>
+        <v>2326105.34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>35429.30</v>
+        <v>6270.32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="2">
-        <v>205707.55</v>
+        <v>39131.27</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2">
-        <v>2213.75</v>
+        <v>41796.66</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2">
-        <v>0.00</v>
+        <v>7576.32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>19497.00</v>
+        <v>2190.53</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -953,10 +953,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2">
-        <v>2499.31</v>
+        <v>14631.95</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>66</v>
@@ -970,7 +970,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>3837.89</v>
+        <v>15533.83</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>67</v>
@@ -978,16 +978,16 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2">
-        <v>6228.32</v>
+        <v>62167.14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -995,10 +995,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>186041.73</v>
+        <v>13096.93</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>68</v>
@@ -1006,16 +1006,16 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2">
-        <v>6028.90</v>
+        <v>19199.95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1023,10 +1023,10 @@
         <v>17</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2">
-        <v>16600.67</v>
+        <v>12267.19</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>69</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2">
-        <v>4722.19</v>
+        <v>17993.69</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1051,10 +1051,10 @@
         <v>18</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2">
-        <v>7921.32</v>
+        <v>8719.58</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>70</v>
@@ -1068,7 +1068,7 @@
         <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>4305.07</v>
+        <v>22081.32</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>71</v>
@@ -1076,114 +1076,114 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>16984.40</v>
+        <v>25737.90</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="2">
-        <v>2089.90</v>
+        <v>6538.07</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C31" s="2">
-        <v>2433.75</v>
+        <v>214263.57</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="2">
-        <v>14041.75</v>
+        <v>19073.80</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2">
-        <v>9496.08</v>
+        <v>6075.27</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C34" s="2">
-        <v>0.00</v>
+        <v>15000.00</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="2">
-        <v>56833.27</v>
+        <v>8369.80</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="2">
-        <v>8452.20</v>
+        <v>52473.31</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1194,7 +1194,7 @@
         <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>50141.18</v>
+        <v>2182.50</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>77</v>
@@ -1208,7 +1208,7 @@
         <v>49</v>
       </c>
       <c r="C38" s="2">
-        <v>13439.63</v>
+        <v>35429.30</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>78</v>
@@ -1222,7 +1222,7 @@
         <v>50</v>
       </c>
       <c r="C39" s="2">
-        <v>2428900.14</v>
+        <v>196384.33</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>78</v>
@@ -1236,7 +1236,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="2">
-        <v>6270.32</v>
+        <v>2213.75</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>79</v>
@@ -1250,7 +1250,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="2">
-        <v>39131.27</v>
+        <v>0.00</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>79</v>
@@ -1261,10 +1261,10 @@
         <v>28</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="2">
-        <v>53734.14</v>
+        <v>3837.89</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>80</v>
@@ -1272,16 +1272,16 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>7576.32</v>
+        <v>6228.32</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1289,10 +1289,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2">
-        <v>2190.53</v>
+        <v>146686.89</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>81</v>
@@ -1300,16 +1300,16 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>15785.37</v>
+        <v>6028.90</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1317,10 +1317,10 @@
         <v>30</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C46" s="2">
-        <v>15533.83</v>
+        <v>16600.67</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>82</v>
@@ -1328,16 +1328,16 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>68914.40</v>
+        <v>4722.19</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1345,10 +1345,10 @@
         <v>31</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" s="2">
-        <v>13096.93</v>
+        <v>7921.32</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>83</v>
@@ -1356,16 +1356,16 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>19199.95</v>
+        <v>4305.07</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1373,10 +1373,10 @@
         <v>32</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" s="2">
-        <v>12267.19</v>
+        <v>16984.40</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>84</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="2">
-        <v>17993.69</v>
+        <v>2089.90</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1401,10 +1401,10 @@
         <v>33</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C52" s="2">
-        <v>8719.58</v>
+        <v>2433.75</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>85</v>
@@ -1415,10 +1415,10 @@
         <v>34</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C53" s="2">
-        <v>13848.00</v>
+        <v>14041.75</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>86</v>
@@ -1426,16 +1426,16 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C54" s="2">
-        <v>72841.13</v>
+        <v>9496.08</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1446,7 +1446,7 @@
         <v>50</v>
       </c>
       <c r="C55" s="2">
-        <v>351124.98</v>
+        <v>0.00</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>87</v>
@@ -1457,10 +1457,10 @@
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C56" s="2">
-        <v>4035.42</v>
+        <v>5103.81</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>88</v>
@@ -1471,10 +1471,10 @@
         <v>36</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>10062.36</v>
+        <v>24178.10</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>88</v>
@@ -1485,10 +1485,10 @@
         <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C58" s="2">
-        <v>352431.60</v>
+        <v>19497.00</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>89</v>
@@ -1496,100 +1496,100 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C59" s="2">
-        <v>21782.34</v>
+        <v>2499.31</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C60" s="2">
-        <v>107460.37</v>
+        <v>13848.00</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="2">
-        <v>28473.89</v>
+        <v>72841.13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C62" s="2">
-        <v>35055.18</v>
+        <v>351124.98</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C63" s="2">
-        <v>4143.75</v>
+        <v>4035.42</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C64" s="2">
-        <v>8106.66</v>
+        <v>10062.36</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C65" s="2">
-        <v>8033.68</v>
+        <v>352431.60</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1600,7 +1600,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="2">
-        <v>22081.32</v>
+        <v>21782.34</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>94</v>
@@ -1611,10 +1611,10 @@
         <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C67" s="2">
-        <v>25737.90</v>
+        <v>100916.35</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>95</v>
@@ -1622,58 +1622,58 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C68" s="2">
-        <v>6538.07</v>
+        <v>28473.89</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C69" s="2">
-        <v>804763.69</v>
+        <v>30114.38</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C70" s="2">
-        <v>19073.80</v>
+        <v>4143.75</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C71" s="2">
-        <v>6075.27</v>
+        <v>8106.66</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1681,10 +1681,10 @@
         <v>46</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="2">
-        <v>15000.00</v>
+        <v>8033.68</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>98</v>
